--- a/data/processed/y_train.xlsx
+++ b/data/processed/y_train.xlsx
@@ -430,12 +430,12 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -445,7 +445,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -455,12 +455,12 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -475,27 +475,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -520,17 +520,17 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -540,7 +540,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -560,7 +560,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -570,17 +570,17 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -600,12 +600,12 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -625,7 +625,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -640,7 +640,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -655,7 +655,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -670,7 +670,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -680,7 +680,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -695,17 +695,17 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -720,7 +720,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -730,17 +730,17 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -775,22 +775,22 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -815,7 +815,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -825,7 +825,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -835,7 +835,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -850,7 +850,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -860,7 +860,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -870,7 +870,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -895,12 +895,12 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -920,12 +920,12 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -945,12 +945,12 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -965,7 +965,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -990,12 +990,12 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -1005,7 +1005,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -1025,7 +1025,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -1035,12 +1035,12 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -1075,7 +1075,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -1100,27 +1100,27 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
@@ -1135,7 +1135,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -1145,7 +1145,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -1160,7 +1160,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -1170,17 +1170,17 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -1190,12 +1190,12 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
@@ -1205,12 +1205,12 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -1225,7 +1225,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
@@ -1235,7 +1235,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -1265,17 +1265,17 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173">
@@ -1295,12 +1295,12 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -1315,7 +1315,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181">
@@ -1330,7 +1330,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -1340,22 +1340,22 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
@@ -1395,7 +1395,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -1405,7 +1405,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -1420,7 +1420,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="202">
@@ -1430,17 +1430,17 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -1450,7 +1450,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208">
@@ -1470,7 +1470,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212">
@@ -1485,12 +1485,12 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -1505,7 +1505,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
@@ -1525,7 +1525,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
@@ -1535,7 +1535,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225">
@@ -1545,17 +1545,17 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229">
@@ -1565,17 +1565,17 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
@@ -1585,7 +1585,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235">
@@ -1610,7 +1610,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
@@ -1620,12 +1620,12 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
@@ -1635,7 +1635,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245">
@@ -1660,7 +1660,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
@@ -1670,12 +1670,12 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253">
@@ -1690,12 +1690,12 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257">
@@ -1710,22 +1710,22 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263">
@@ -1745,7 +1745,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="267">
@@ -1785,12 +1785,12 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276">
@@ -1800,7 +1800,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="278">
@@ -1815,7 +1815,7 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="281">
@@ -1830,17 +1830,17 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="286">
@@ -1875,7 +1875,7 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="293">
@@ -1910,7 +1910,7 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300">
@@ -1930,12 +1930,12 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="305">
@@ -1960,7 +1960,7 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="310">
@@ -1970,7 +1970,7 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312">
@@ -1980,7 +1980,7 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314">
@@ -1990,17 +1990,17 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318">
@@ -2010,7 +2010,7 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320">
@@ -2025,7 +2025,7 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323">
@@ -2045,7 +2045,7 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327">
@@ -2070,7 +2070,7 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332">
@@ -2085,7 +2085,7 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335">
@@ -2095,7 +2095,7 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="337">
@@ -2115,7 +2115,7 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341">
@@ -2135,12 +2135,12 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="346">
@@ -2150,12 +2150,12 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="349">
@@ -2170,17 +2170,17 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="354">
@@ -2190,12 +2190,12 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="357">
@@ -2205,7 +2205,7 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="359">
@@ -2225,12 +2225,12 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="364">
@@ -2240,7 +2240,7 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="366">
@@ -2250,7 +2250,7 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="368">
@@ -2265,12 +2265,12 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="372">
@@ -2280,7 +2280,7 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="374">
@@ -2335,7 +2335,7 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="385">
@@ -2355,7 +2355,7 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="389">
@@ -2365,17 +2365,17 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="393">
@@ -2385,7 +2385,7 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="395">
@@ -2395,7 +2395,7 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="397">
@@ -2405,7 +2405,7 @@
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="399">
@@ -2415,17 +2415,17 @@
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="403">
@@ -2470,7 +2470,7 @@
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="412">
@@ -2480,22 +2480,22 @@
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="417">
@@ -2510,12 +2510,12 @@
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="421">
@@ -2525,17 +2525,17 @@
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="425">
@@ -2550,7 +2550,7 @@
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="428">
@@ -2560,7 +2560,7 @@
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="430">
@@ -2575,27 +2575,27 @@
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="437">
@@ -2605,7 +2605,7 @@
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="439">
@@ -2630,12 +2630,12 @@
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="445">
@@ -2650,7 +2650,7 @@
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="448">
@@ -2670,22 +2670,22 @@
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="455">
@@ -2695,12 +2695,12 @@
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="458">
@@ -2710,17 +2710,17 @@
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="462">
@@ -2730,17 +2730,17 @@
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="466">
@@ -2750,22 +2750,22 @@
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="471">
@@ -2790,12 +2790,12 @@
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="477">
@@ -2805,7 +2805,7 @@
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="479">
@@ -2825,7 +2825,7 @@
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="483">
@@ -2835,7 +2835,7 @@
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="485">
@@ -2850,7 +2850,7 @@
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="488">
@@ -2870,7 +2870,7 @@
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="492">
@@ -2885,7 +2885,7 @@
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="495">
@@ -2900,7 +2900,7 @@
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="498">
@@ -2910,7 +2910,7 @@
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="500">
@@ -2930,17 +2930,17 @@
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="506">
@@ -2950,7 +2950,7 @@
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="508">
@@ -2970,17 +2970,17 @@
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="514">
@@ -2995,17 +2995,17 @@
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="519">
@@ -3020,12 +3020,12 @@
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="523">
@@ -3050,22 +3050,22 @@
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="531">
@@ -3075,7 +3075,7 @@
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="533">
@@ -3090,7 +3090,7 @@
     </row>
     <row r="535">
       <c r="A535" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="536">
@@ -3100,7 +3100,7 @@
     </row>
     <row r="537">
       <c r="A537" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="538">
@@ -3110,17 +3110,17 @@
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="542">
@@ -3140,7 +3140,7 @@
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="546">
@@ -3150,7 +3150,7 @@
     </row>
     <row r="547">
       <c r="A547" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="548">
@@ -3160,7 +3160,7 @@
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="550">
@@ -3170,7 +3170,7 @@
     </row>
     <row r="551">
       <c r="A551" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="552">
@@ -3210,7 +3210,7 @@
     </row>
     <row r="559">
       <c r="A559" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="560">
@@ -3225,7 +3225,7 @@
     </row>
     <row r="562">
       <c r="A562" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="563">
@@ -3235,7 +3235,7 @@
     </row>
     <row r="564">
       <c r="A564" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="565">
@@ -3245,17 +3245,17 @@
     </row>
     <row r="566">
       <c r="A566" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="569">
@@ -3265,7 +3265,7 @@
     </row>
     <row r="570">
       <c r="A570" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="571">
@@ -3280,12 +3280,12 @@
     </row>
     <row r="573">
       <c r="A573" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="575">
@@ -3320,12 +3320,12 @@
     </row>
     <row r="581">
       <c r="A581" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="583">
@@ -3350,7 +3350,7 @@
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="588">
@@ -3360,12 +3360,12 @@
     </row>
     <row r="589">
       <c r="A589" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="591">
@@ -3375,7 +3375,7 @@
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="593">
@@ -3385,7 +3385,7 @@
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="595">
@@ -3395,7 +3395,7 @@
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="597">
@@ -3420,7 +3420,7 @@
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="602">
@@ -3435,7 +3435,7 @@
     </row>
     <row r="604">
       <c r="A604" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="605">
@@ -3445,12 +3445,12 @@
     </row>
     <row r="606">
       <c r="A606" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="608">
@@ -3470,7 +3470,7 @@
     </row>
     <row r="611">
       <c r="A611" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="612">
@@ -3485,12 +3485,12 @@
     </row>
     <row r="614">
       <c r="A614" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
